--- a/results/day_tractor/shallow/SVM/all_results_svm.xlsx
+++ b/results/day_tractor/shallow/SVM/all_results_svm.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3505,6 +3505,127 @@
       </c>
       <c r="AK25" t="n">
         <v>0.6588216601039006</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-24_16-18-41</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>42</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>72.15177748314311</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.2194704913043539</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>21</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9937.740738236927</v>
+      </c>
+      <c r="M26" t="n">
+        <v>38560</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.7593164016140518</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8418188604857175</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.7593164016140518</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.7934024883141519</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.8578670371872288</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6609506690632746</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.7213068956878915</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.6759295391854732</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.6905191633931416</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.6727409107248429</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.6905191633931416</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.6777294618529985</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.8134903577325802</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.5604227913919527</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.5647759703236018</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.5543855338085703</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.755649145541427</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.7480450312929088</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.755649145541427</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.7402123990925663</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.8648427774412154</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.6310729859957629</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.6439520156898589</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.6179322383062137</v>
       </c>
     </row>
   </sheetData>

--- a/results/day_tractor/shallow/SVM/all_results_svm.xlsx
+++ b/results/day_tractor/shallow/SVM/all_results_svm.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3626,6 +3626,3878 @@
       </c>
       <c r="AK26" t="n">
         <v>0.6179322383062137</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-24_19-05-55</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>42</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7803884850277908</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.763079998696547</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>26</v>
+      </c>
+      <c r="L27" t="n">
+        <v>225.3264967490686</v>
+      </c>
+      <c r="M27" t="n">
+        <v>34295</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.7547200036615787</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.9148435018378993</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.7547200036615787</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.8134011297712703</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.9150943066504519</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.796156544645474</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.8839165229596796</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.8110404478597815</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.6447506714936354</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.7299921641753148</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.6447506714936354</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.6682837778830649</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.8028825777423364</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.6681844364765905</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.6451575511247482</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.6218615873240275</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.711032519623911</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.7801736955355117</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.711032519623911</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.7312393167733142</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.8400775038154801</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.6562469299342548</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.6820330605109458</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.6221904742055698</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-24_19-13-00</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>42</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.543941231681779</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.41780035302378</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>29</v>
+      </c>
+      <c r="L28" t="n">
+        <v>194.7612326440867</v>
+      </c>
+      <c r="M28" t="n">
+        <v>29283</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.8191484356621971</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.9494790830034705</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.8191484356621971</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.8678296364801628</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.9612487379845419</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.8372591285348187</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.9244087175849677</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.8467382567028011</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.6769079513334153</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.7386389587425655</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.6769079513334153</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.6941988417164648</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.8052174247007182</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.6731462374852519</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.6154470155410851</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.598381729179007</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.7487060503301802</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.7967674538832097</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.7487060503301802</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.7602782333904865</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.8457011091171363</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.6731570653637768</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.6472882165174164</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.6036840899427479</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-24_19-19-01</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>42</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.550088256963294</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.186880998419379</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>41</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3115.88585323398</v>
+      </c>
+      <c r="M29" t="n">
+        <v>28771</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.7333890408183936</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.9711920023436577</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.7333890408183936</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.8277434638969662</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.9660239391240221</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.776612892221205</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.8674870339983775</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.7727272326275454</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.7010547608727062</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.7585854522416667</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.7010547608727062</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.723971374356148</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.7976684061879294</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.4605156352797827</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.4765232526049756</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.4554627363753961</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.7958234362628662</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.8520149066758251</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.7958234362628662</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.8089893096006266</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.856031218885232</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.6548101288460922</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.6125492622337583</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.5056577830355909</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-24_20-13-33</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>42</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.56138074153559</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.07417077580505224</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>25</v>
+      </c>
+      <c r="L30" t="n">
+        <v>271.2217040499672</v>
+      </c>
+      <c r="M30" t="n">
+        <v>31119</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.812538219373542</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.9292095376835022</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.812538219373542</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.8541540219204865</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.9464069297155944</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.8455592113717185</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.9197854155160295</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.8566670205013427</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.6647544745296007</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.7208499253772496</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.6647544745296007</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.6813244245208624</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.8038552447729895</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.6672924730680809</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.6324458022790468</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.6236311992541145</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.7329695626225595</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.7808306224966627</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.7329695626225595</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.7455800119354251</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.849638032240105</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.6680630678845545</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.6868326041635983</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.642273464498651</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-24_20-20-55</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>42</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7849590083353899</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.5127370874628439</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>sigmoid</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>34</v>
+      </c>
+      <c r="L31" t="n">
+        <v>382.0284747969126</v>
+      </c>
+      <c r="M31" t="n">
+        <v>27196</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.4156360531772167</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.8490661496719006</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.4156360531772167</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.5472965460690867</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.9133495897661418</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.2409303859494717</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.2618263545056616</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.1734644562132514</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.4627123142250531</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.6767490550596655</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.4627123142250531</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.5200102923738951</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.7770930381332033</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.3345013957823422</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.2922539590184834</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.2621594380075131</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.3537019681349578</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.61285051545328</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.3537019681349578</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.4174002314033748</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.8105656373764047</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.2213384362646413</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.2565535120674551</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.1844628431133128</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-24_20-29-35</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>42</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.042943346173951</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1969043480269281</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>45</v>
+      </c>
+      <c r="L32" t="n">
+        <v>120.2581817749888</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10613</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.9935362587556654</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9958373210321629</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9935362587556654</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.9942312424352454</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.9999376014484388</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.9162577239186515</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.9985266494482273</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.9486657169619261</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.8597230583985551</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.7945983139369718</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.8597230583985551</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.8212620574025803</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.8217702098862534</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.5348236910972175</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.5293629108766413</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.5171541203828638</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8725390704282525</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.86019870383176</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.8725390704282525</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.8539193524583</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.8432020861245376</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.5026769951670768</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.5769169915197411</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.5029694312308385</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-24_20-32-47</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>42</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>47.39909667656128</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.621693800759638</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>30</v>
+      </c>
+      <c r="L33" t="n">
+        <v>377.7973316290881</v>
+      </c>
+      <c r="M33" t="n">
+        <v>21009</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.9308578745198464</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.971531408224635</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.9308578745198464</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.9450104755929377</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.9939166348472446</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.8906485971682906</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.9738221572562535</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.910646534687789</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.7463768115942029</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.7455231642693831</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.7463768115942029</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.736451738275227</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.7971362047476866</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.6855777440214527</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.6020672364490868</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.590437129244724</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.7795708618824377</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.7924256995549168</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.7795708618824377</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.7742344606408837</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.833314642335121</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.6760294899645048</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.6213417707473629</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.5920228756293948</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-24_20-41-12</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>42</v>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13.89069254026063</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9.920670368929654</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>sigmoid</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>50</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2441.558512479998</v>
+      </c>
+      <c r="M34" t="n">
+        <v>38117</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.005929112994202062</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.515438089801574e-05</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.005929112994202062</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6.989435029547328e-05</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.03355111816879325</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.001185822598840412</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.00235766632762173</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.01533354410369902</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.000235117574780083</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.01533354410369902</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.0004631336690203347</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.178623421610716</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.002555590683949836</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.005033992423062951</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.001979991663192997</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>3.920366986313771e-06</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.001979991663192997</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>7.825240062541225e-06</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.1235558693662727</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.0003299986105321662</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.0006586930143872421</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-24_21-27-53</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>42</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3072407411146645</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.7025523533015083</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>30</v>
+      </c>
+      <c r="L35" t="n">
+        <v>270.9882892839378</v>
+      </c>
+      <c r="M35" t="n">
+        <v>32867</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.7811684924360981</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.9399990487678744</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.7811684924360981</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.8421633594768343</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.9385149874490977</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.7710850159695845</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.8904310177544099</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.7950237376541976</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.6651674162918541</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.7440372053932753</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.6651674162918541</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.6886325146488821</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.8125580255042503</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.648278313145766</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.6013892076825765</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.5822137504576741</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.7404435629282365</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.8070714857885793</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.7404435629282365</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.7583976050693958</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.8481230130552329</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.6501586772256861</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.6613361438726612</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.5909914761430598</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-24_21-34-44</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>42</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.714707988944772</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0262976993809375</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>33</v>
+      </c>
+      <c r="L36" t="n">
+        <v>672.8579519650666</v>
+      </c>
+      <c r="M36" t="n">
+        <v>32236</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.7388638456691387</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.9419390836668694</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.7388638456691387</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.8177509745436474</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.9362087036584916</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.6240452216228807</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.8331882105532307</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.6506975053345676</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.6950039236201936</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.7277848488477745</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.6950039236201936</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.705585396660288</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.8088890542510594</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.5254430741299602</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.5127061739954576</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.4918222391707751</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.7754154674589174</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.8107319149443902</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.7754154674589174</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.7820867484704886</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.8581806092284543</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.5690557620613416</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.6216085279574606</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.5465367607385433</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-24_21-47-54</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>42</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.294182951069526</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.466110818406086</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>sigmoid</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>19</v>
+      </c>
+      <c r="L37" t="n">
+        <v>245.7819937100867</v>
+      </c>
+      <c r="M37" t="n">
+        <v>33333</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.3418331030440062</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.6854323764190688</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3418331030440062</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4251823132571049</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.8043484504953029</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.2308765382070015</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.1991139284746311</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.1651475953819762</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.398044408229782</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.5169407362113365</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.398044408229782</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.4275295963539265</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.7485078522364156</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.2146244946991661</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.2442624365229492</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.2112532046478418</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.317792279267238</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.4636613890136265</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.317792279267238</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.3491172630891146</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.7938497889049433</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.1890782622531324</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.221988299621914</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.1751622600241664</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-24_21-54-12</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>42</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>36.93261231099635</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.01084282010930624</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>44</v>
+      </c>
+      <c r="L38" t="n">
+        <v>13855.44184939901</v>
+      </c>
+      <c r="M38" t="n">
+        <v>27352</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.7184702593172083</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.9777920140136429</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.7184702593172083</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.8207129355645214</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.972920196877579</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.752472701687502</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.8475213030828798</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.7376699275443104</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.6914481525625745</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.7715185885526471</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.6914481525625745</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.7236408027430454</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.7896147261132451</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.4668893260204887</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.47777882543273</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.4586708288686593</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.7792797336830425</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.8541589082865413</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.7792797336830425</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.8031335517174769</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.8465430050035392</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.4752887142177926</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.5914210753317255</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.4830190892640984</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-25_01-47-32</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>42</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.65687250050888</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.01455505882555169</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" t="n">
+        <v>316.564334422932</v>
+      </c>
+      <c r="M39" t="n">
+        <v>45923</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.7063036042259929</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.7639506684791533</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.7063036042259929</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.7230213503768228</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.8424598208857353</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.8023831207779694</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.8518024274764393</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.8169377311445297</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.6481258527971747</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.6860370459438084</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.6481258527971747</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.6565588984619455</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.8159229296305668</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.6610945191271763</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.7060751129631381</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.6754059942635747</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.6775596257741467</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.7141687494801675</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.6775596257741467</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.6862295649409214</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.834980815103664</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.6796573696007192</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.7140414713903461</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.6778735541191138</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-25_01-57-00</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>42</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>24.04878335900933</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.04696497161394395</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>18</v>
+      </c>
+      <c r="L40" t="n">
+        <v>259.424166980898</v>
+      </c>
+      <c r="M40" t="n">
+        <v>34246</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.7919247628259214</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.8837872346692124</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.7919247628259214</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.8212726689191339</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.919525052903916</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.8564002529311977</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.9133965487708323</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.8691479631696494</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.6638429340243173</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.7115647415007721</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.6638429340243173</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.677467036703734</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.8234192302913177</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.6615844877695904</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.6611061384153304</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.649966179547388</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.7110027855153204</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.7597049331799016</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.7110027855153204</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.7234471876763271</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.8440247796394231</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.6741003994218332</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.7037056164209078</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.6664473173669254</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-25_02-04-07</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>42</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.16547042568039</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.243534415343301</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>46</v>
+      </c>
+      <c r="L41" t="n">
+        <v>129.6528643629281</v>
+      </c>
+      <c r="M41" t="n">
+        <v>11159</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.9729855492076622</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.992476953992499</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.9729855492076622</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.9804823225395921</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.9998031864212673</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.8371355720870284</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.993851132686084</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.8721776848944469</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.8479781088476741</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.8052703346698123</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.8479781088476741</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.8232181688559201</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.8351577496359294</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.543387356246772</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.5436835093364043</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.5257398383464377</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8703061224489796</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.864787205780374</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.8703061224489796</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.8585590762451246</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.8353519471809526</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.5076139969576693</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.5622749653821716</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.5114475029127342</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-25_02-08-13</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>42</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>94.88317236795463</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0633559800884045</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>40</v>
+      </c>
+      <c r="L42" t="n">
+        <v>248.1102072159993</v>
+      </c>
+      <c r="M42" t="n">
+        <v>14791</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.8745557655954631</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.9855088404000431</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.8745557655954631</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.9199295679853139</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.9921039665915402</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.8510235233811289</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.9700965785966784</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.8524566491357843</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.7414557414557414</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.7793671406222377</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.7414557414557414</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.7558035493024091</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.8060872980084376</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.5332030775634132</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.5532594882486853</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.5344609460831871</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.7942795360723413</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.843960758857657</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.7942795360723413</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.8054336828210882</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.8328648944464803</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.659913885899751</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.570677574187895</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.5039096624890761</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-25_02-13-33</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>42</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>17.88680353792664</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.824728966705541</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>12</v>
+      </c>
+      <c r="L43" t="n">
+        <v>267.5395986579824</v>
+      </c>
+      <c r="M43" t="n">
+        <v>40935</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.7427649852163785</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.8092980820725438</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.7427649852163785</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.7620605890343704</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.873055537972756</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.8355649321262705</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.8870564943937618</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.8515663929314953</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.6677755032412146</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.7072715059298645</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.6677755032412146</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.6770478734335792</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.8332545971740093</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.6656020427323119</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.7032552803676548</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.6768776496772868</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.6864301490889012</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.7286882694033739</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.6864301490889012</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.6962217117804856</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.8446282957075049</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.6771016865670311</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.7113012002500296</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.6758572345912955</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-25_02-21-25</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>42</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3618920291309286</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.80953050813684</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>37</v>
+      </c>
+      <c r="L44" t="n">
+        <v>342.9587015910074</v>
+      </c>
+      <c r="M44" t="n">
+        <v>23274</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.8134044929874643</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.976355501587288</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.8134044929874643</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.8780858704350052</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.9805920367746696</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.8301907819247961</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.9390289749600421</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.8304502167574683</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.6831997789444598</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.7726300959315644</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.6831997789444598</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.7108445964490971</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.8115597576712444</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.6046136313308248</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.5358267231295395</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.5058660137348732</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.76375</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.8319061927577923</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.76375</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.7832737141722226</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.8397665383944499</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.6140522642084214</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.5921367370130994</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.521222655427798</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-25_02-28-45</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>42</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11.00611569060163</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.01802547415669562</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>16</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1399.406681656023</v>
+      </c>
+      <c r="M45" t="n">
+        <v>42860</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.7307365130863123</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.7729606455531978</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.7307365130863123</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.7489590380220024</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.8263097633300034</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.6565534984888447</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.6870289975297821</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.6677299013346735</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.6594995718770812</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.647849855182685</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.6594995718770812</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.6443987076720834</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.8163574328357401</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.5473148632734898</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.5529252649063624</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.5326123998787633</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.7159311892296185</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0.7153870985318289</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0.7159311892296185</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.6976245207420718</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0.8586010031114245</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0.6135631142891902</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.6202092976996741</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.5810199808070095</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-25_02-53-29</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>42</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>43.95554676222922</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8.495973708503703</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>31</v>
+      </c>
+      <c r="L46" t="n">
+        <v>9150.498617489939</v>
+      </c>
+      <c r="M46" t="n">
+        <v>32875</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.7642406575551945</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.9302270747851353</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.7642406575551945</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.8304477427011488</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.9253783676256279</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.6348744903832116</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.8076653127344852</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.6637646006736261</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.7061809874349537</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.7173191338530059</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.7061809874349537</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.7072104480814417</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.8078027622941482</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.5292404459413652</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.5133871579629066</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.4962942734501499</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.7826443270806774</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.8009114348731187</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.7826443270806774</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.7818603305375253</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.8589798644327452</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0.5920059188877461</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0.6296953849396024</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.5671732048181796</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-25_05-28-34</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>42</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>17.04133586324829</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.2727652098028407</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>sigmoid</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>27</v>
+      </c>
+      <c r="L47" t="n">
+        <v>191.621426452999</v>
+      </c>
+      <c r="M47" t="n">
+        <v>24643</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.4411880272737779</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.8107877658371719</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.4411880272737779</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.5503150350568582</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.8338072809134421</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.2482459408242155</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.2794861748545411</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.192376723721104</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.4508079847908745</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.6227882535066922</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.4508079847908745</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.4882522941011066</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.7148961541702575</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.2833479608298671</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.2963113869978083</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0.2503642537492076</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.4380453752181501</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.5920571540117953</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.4380453752181501</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.4750197372290696</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0.7224353016326375</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.2275944961618831</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0.3039962761269716</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.2258301431679115</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-25_05-33-25</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>42</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>93.54419504216871</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.04473948217802783</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>40</v>
+      </c>
+      <c r="L48" t="n">
+        <v>176.9039105470292</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7014</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.9973534971644612</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.997739445494644</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.9973534971644612</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.9974555560549675</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.9999629790978626</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.9756944444444443</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.9994926653910824</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.9866373317922085</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.8444158444158444</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.7706407836505023</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.8444158444158444</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.801581886010453</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.8160249245694591</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.5208644273385052</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.550391574694271</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.5238820811198103</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.859740515038333</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0.8351128475960202</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0.859740515038333</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0.8335019400772754</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0.8335842137421008</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0.5113706779245051</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0.5497979990642176</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.4959280528623048</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-25_05-37-37</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>42</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.4871446858132878</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.413226300006937</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>sigmoid</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>39</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1916.026400981005</v>
+      </c>
+      <c r="M49" t="n">
+        <v>39868</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.9110815691782883</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.8634533360590684</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.9110815691782883</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.8815097312009376</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.9394970665995023</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.2286638227234011</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.3317918432905515</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.2590032794444673</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.7983026874115983</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.6716537821178541</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.7983026874115983</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.7241810234701258</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.777597092653309</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.1993545663962208</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.2369662189982682</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8370095647081788</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.7358844741106408</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.8370095647081788</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.7826954757577367</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0.8090749872197617</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0.2613141081112265</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.284865540963102</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.2722286577172142</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-25_06-14-44</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>42</v>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>31.12758055524998</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.7708067883918879</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>sigmoid</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>23</v>
+      </c>
+      <c r="L50" t="n">
+        <v>177.6299036470009</v>
+      </c>
+      <c r="M50" t="n">
+        <v>28671</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.368659921627665</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.7477604733703302</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.368659921627665</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.4688986211933728</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.7942190357510629</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.2645070803935589</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.207980226654198</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.1678592750463627</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.4199823165340407</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.546391643284588</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.4199823165340407</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.4538344788184935</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.7134386929983808</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.2208505808755368</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.2487176244939468</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0.213616119492653</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.3301729873586161</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.5028646048215597</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.3301729873586161</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.3681754006955008</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0.7247987618764187</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0.1936708781255814</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0.2295092073054557</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0.1745255081173015</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-25_06-19-33</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>42</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>45.29111148855568</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.095565554516481</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>46</v>
+      </c>
+      <c r="L51" t="n">
+        <v>102.8196538989432</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5215</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.9991210609311584</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.9991959579946688</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.9991210609311584</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.9991403985664827</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.9999977431698799</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.9829573934837093</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.9997999411591645</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.9909993969649135</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.8750380054727881</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.8025254517674776</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.8750380054727881</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.8318534100031614</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.8307861982896587</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.5400581532300703</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.5410402277409398</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0.5178071778538799</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8863265306122449</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0.8654586824493786</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0.8863265306122449</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.864398487546685</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0.8349205435741458</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0.5114232817576559</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0.5597844895550371</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0.5046052441059067</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-25_06-22-37</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>42</v>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>69.5203214369682</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.557999881521363</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>28</v>
+      </c>
+      <c r="L52" t="n">
+        <v>449.3280114099616</v>
+      </c>
+      <c r="M52" t="n">
+        <v>21885</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.9286997084548105</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.9661129507901122</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.9286997084548105</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.9415148299778561</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.9914401090291864</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.8957932253354796</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.9691851140084454</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0.9153280656806634</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.7361933534743202</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.733429544804322</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.7361933534743202</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.726496822110876</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.7967670493424558</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.6808215032426377</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.6129869623622006</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.606058827837736</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.7729920564872022</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0.7844835023478804</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.7729920564872022</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0.7680111746261188</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0.835288057984705</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0.6787623537092268</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0.6416265579775274</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0.6161425772639795</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-25_06-32-13</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>42</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.585932759723227</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0119395553763358</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>15</v>
+      </c>
+      <c r="L53" t="n">
+        <v>517.3141571109882</v>
+      </c>
+      <c r="M53" t="n">
+        <v>44065</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.7267592556772022</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.7598235043887738</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.7267592556772022</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.7412436032767801</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.8211552364443913</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.6703679489187494</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.6979644713615371</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.6809219371311864</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.6596553002223869</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.6472747850771412</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.6596553002223869</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.6438772168037515</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.8186313035920405</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.5579108057354234</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.566210192550329</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.5464208700688024</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.7147367648138629</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0.7133773930073263</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0.7147367648138629</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0.6950196588652998</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0.8583290091190738</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0.6234752027549747</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0.6279577290975283</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0.5936439321360224</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-25_06-42-44</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>42</v>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.458817373493798</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.06805908701019697</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>rbf</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>49</v>
+      </c>
+      <c r="L54" t="n">
+        <v>153.9817249650368</v>
+      </c>
+      <c r="M54" t="n">
+        <v>13421</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.9592471572343485</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.9930581054855935</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.9592471572343485</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.9733803844961288</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.9998173801911298</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.8075546590317544</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.990760933981273</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.8365768923986968</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.8517300767183341</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.8202810873938178</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.8517300767183341</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.8320753458321951</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.8428825363521595</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.5580847496649467</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.5369306895759239</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.5188763317536761</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8673786810452094</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0.8791046325293698</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0.8673786810452094</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0.8647925952915947</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0.8304607918131476</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0.5080783536106946</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0.5877894646316024</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0.5179821464830533</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-25_06-47-29</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>42</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.2252140953021269</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.3565638590821157</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>37</v>
+      </c>
+      <c r="L55" t="n">
+        <v>308.6985552830156</v>
+      </c>
+      <c r="M55" t="n">
+        <v>31323</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.7363783045798684</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.9580687147949785</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.7363783045798684</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.8233218975189918</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.9534591407957547</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.6408966513194049</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.8552290123877367</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.6721802060269221</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.7040618955512572</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.7488574494799413</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.7040618955512572</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.719733544826475</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.8091087672848308</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.5072180208196283</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.5013279918236786</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.4742576154996421</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.7826923076923077</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0.8291741971108734</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0.7826923076923077</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0.7929044470302815</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0.8615346668293481</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0.5440673234847565</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0.6087364199960925</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0.5036033644753819</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-25_06-55-50</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>42</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.542336400433376</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.4968942092731392</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>sigmoid</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>40</v>
+      </c>
+      <c r="L56" t="n">
+        <v>400.1890373700298</v>
+      </c>
+      <c r="M56" t="n">
+        <v>26218</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.3791052299936988</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8746304968881431</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.3791052299936988</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.5211954789542452</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.9460819556925633</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.2430064936140076</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.3798834457298355</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.1654438014302635</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.462033462033462</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.690122714683081</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.462033462033462</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.5336516140316335</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.8035130107457881</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.2560335867258896</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.2691560247977562</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.2399449739822115</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.3316296441910753</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0.7081335066999288</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.3316296441910753</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.4141891008539043</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0.8298631432943979</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0.2755175758012537</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0.2415171859965319</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0.1669854550950347</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-25_07-05-13</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>42</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.911848946144795</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.1166375029847802</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>33</v>
+      </c>
+      <c r="L57" t="n">
+        <v>244.3702855389565</v>
+      </c>
+      <c r="M57" t="n">
+        <v>29304</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.7843536425767049</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.956618182733195</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.7843536425767049</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.8516278114521344</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.9548896091350977</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.8091122072457092</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.9009780250764048</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.8148057444905854</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.6590374051791786</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.7555806704697674</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.6590374051791786</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.6878411657339714</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.8087251021020606</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.6425859759593193</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.5752751775766269</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.5510334372846528</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.7341008262928234</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0.8125203200894926</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0.7341008262928234</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0.7564290452993676</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0.8472966173235871</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0.6428714647133266</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.6188704121649989</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0.5510880457850269</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-25_07-11-12</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>42</v>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.1895782436203598</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.04491087102885092</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>sigmoid</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>26</v>
+      </c>
+      <c r="L58" t="n">
+        <v>365.2124397560256</v>
+      </c>
+      <c r="M58" t="n">
+        <v>41496</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.5450030894569421</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.7982614577306189</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.5450030894569421</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.6361513922260588</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.8420160179938108</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.2564062828788797</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.2810684440127789</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0.2207823774920129</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.5513254700455448</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.6027323360500733</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.5513254700455448</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.5660907133345047</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.7381731825514763</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.3134881487945281</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.2953122042222296</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0.2716131150169969</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.5029759337531269</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0.5587792491876349</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0.5029759337531269</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0.5207200745388971</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0.7598459864676707</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0.2187573789514314</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0.278867988768099</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0.2312049938618691</v>
       </c>
     </row>
   </sheetData>
